--- a/assets/constructions/examples/ctd_bs_head.xlsx
+++ b/assets/constructions/examples/ctd_bs_head.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,11 +604,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHE MB32-32-53 H</t>
+          <t>BHE MB14-14-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,18 +638,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BHE MB-H</t>
+          <t>BHE MB</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>IH-C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -640,22 +658,24 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="P2" t="n">
         <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>30</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>0.002</v>
@@ -672,12 +692,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>DAN_MB32</t>
+          <t>DAN_MB14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>DAN_CART_IH14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -691,11 +711,9 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>12000</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -705,11 +723,17 @@
           <t>2020 / Iscar website</t>
         </is>
       </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DCK3-FBH32</t>
+          <t>DCK7-DBH160204-T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -719,7 +743,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -731,43 +755,41 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>53</v>
-      </c>
+      <c r="O3" t="n">
+        <v>160</v>
+      </c>
+      <c r="P3" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>87</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER_DCK:7</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>DER_FBH:32</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>TP0902RH</t>
-        </is>
-      </c>
+          <t>DER_D.CC160204-T</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>DEREK</t>
@@ -776,7 +798,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>0.31</v>
+        <v>5.8</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -786,64 +808,50 @@
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
       </c>
+      <c r="AJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BHR MB16-16X34</t>
+          <t>ABH19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BHR MB</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>IH-C</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>34</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -854,42 +862,52 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>DAN_MB16</t>
+          <t>DER_DCK:1</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>DAN_CART_IH16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>DER_A.CC:20/25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>DANDREA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2020 / Iscar website</t>
-        </is>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>133.12</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>10912.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DCK6-DBH6892-C</t>
+          <t>DCK6-FBH63</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -911,29 +929,27 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>68</v>
-      </c>
-      <c r="P5" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>63</v>
+      </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>71</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.002</v>
+      </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -942,10 +958,14 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>DER_D.CC6892-C</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+          <t>DER_FBH:63</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>TP1103RH</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>DEREK</t>
@@ -954,7 +974,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -963,12 +983,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>861.61</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>70629.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DCK5-CBH53-95</t>
+          <t>DCK7-DBH120164-C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -977,7 +1011,9 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>90</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -987,29 +1023,23 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>53</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="P6" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>53</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -1020,19 +1050,15 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>DER_DCK:5</t>
+          <t>DER_DCK:7</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>DER_CBH:5</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>TC1102H</t>
-        </is>
-      </c>
+          <t>DER_D.CC120164-C</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>DEREK</t>
@@ -1041,7 +1067,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1050,6 +1076,20 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>460.76</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>37770.29</v>
       </c>
     </row>
   </sheetData>
